--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>121369</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.419999986886978</v>
+        <v>0.421000003814697</v>
       </c>
       <c r="D2718" t="n">
         <v>0.404000014066696</v>
@@ -62883,6 +62883,29 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>57935</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.41100001335144</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>109650</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.41100001335144</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.41100001335144</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.400999993085861</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>59995</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>128342</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.393999993801117</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>245551</v>
+        <v>177298</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.428999990224838</v>
+        <v>0.43299999833107</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.409999996423721</v>
+        <v>0.405000001192093</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.41100001335144</v>
+        <v>0.43299999833107</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.423000007867813</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>73116</v>
+        <v>245551</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.428000003099442</v>
+        <v>0.428999990224838</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.412999987602234</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.428000003099442</v>
+        <v>0.41100001335144</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.412999987602234</v>
+        <v>0.423000007867813</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>27441</v>
+        <v>73116</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.41100001335144</v>
+        <v>0.428000003099442</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.40599998831749</v>
+        <v>0.412999987602234</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.409999996423721</v>
+        <v>0.428000003099442</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.409999996423721</v>
+        <v>0.412999987602234</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>121369</v>
+        <v>27441</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.421000003814697</v>
+        <v>0.41100001335144</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.404000014066696</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.407000005245209</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.421000003814697</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>57935</v>
+        <v>121369</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.412999987602234</v>
+        <v>0.421000003814697</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.407999992370605</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.412999987602234</v>
+        <v>0.407000005245209</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.41100001335144</v>
+        <v>0.421000003814697</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>109650</v>
+        <v>57935</v>
       </c>
       <c r="C2720" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="F2720" t="n">
         <v>0.41100001335144</v>
-      </c>
-      <c r="D2720" t="n">
-        <v>0.398999989032745</v>
-      </c>
-      <c r="E2720" t="n">
-        <v>0.41100001335144</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>0.400999993085861</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>59995</v>
+        <v>109650</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.400000005960464</v>
+        <v>0.41100001335144</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.389999985694885</v>
+        <v>0.398999989032745</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.400000005960464</v>
+        <v>0.41100001335144</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.395999997854233</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>128342</v>
+        <v>59995</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.409999996423721</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.393999993801117</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="E2722" t="n">
         <v>0.400000005960464</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.404000014066696</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>175028</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.409000009298325</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.388999998569489</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.409000009298325</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>22583</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.39300000667572</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.39300000667572</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>18948</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.393999993801117</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>89231</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.381000012159348</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.381000012159348</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>14682</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>55664</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.372999995946884</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.372999995946884</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.382999986410141</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.382999986410141</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.370000004768372</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.368000000715256</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>21304</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.379000008106232</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.379000008106232</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.377999991178513</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>50366</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.379000008106232</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.377999991178513</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.368999987840652</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>11360</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.361000001430511</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.377999991178513</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.372000008821487</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>19760</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.367000013589859</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.368000000715256</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71667,6 +71667,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>72781</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.35699999332428</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.340999990701675</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.35699999332428</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -71678,7 +71678,7 @@
         <v>0.35699999332428</v>
       </c>
       <c r="D2743" t="n">
-        <v>0.340999990701675</v>
+        <v>0.340000003576279</v>
       </c>
       <c r="E2743" t="n">
         <v>0.35699999332428</v>
@@ -71690,6 +71690,32 @@
         <v>0.34400001168251</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>63033</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.347000002861023</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.347000002861023</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.312999993562698</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.321000009775162</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.321000009775162</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>202818</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.326999992132187</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>102165</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.31700000166893</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.342999994754791</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.342999994754791</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>166401</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80023,7 +80023,7 @@
         <v>0.328999996185303</v>
       </c>
       <c r="D2747" t="n">
-        <v>0.330000013113022</v>
+        <v>0.342999994754791</v>
       </c>
       <c r="E2747" t="n">
         <v>0.31700000166893</v>
@@ -80035,9 +80035,38 @@
         <v>0.342999994754791</v>
       </c>
       <c r="H2747" t="n">
-        <v>166401</v>
+        <v>166728</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.321000009775162</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.321000009775162</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>201367</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80052,7 +80052,7 @@
         <v>0.321000009775162</v>
       </c>
       <c r="D2748" t="n">
-        <v>0.345999985933304</v>
+        <v>0.349999994039536</v>
       </c>
       <c r="E2748" t="n">
         <v>0.321000009775162</v>
@@ -80067,6 +80067,35 @@
         <v>201367</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>156900</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.342000007629395</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.342000007629395</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.349000006914139</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>64075</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80110,7 +80110,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="D2750" t="n">
-        <v>0.342000007629395</v>
+        <v>0.349000006914139</v>
       </c>
       <c r="E2750" t="n">
         <v>0.335999995470047</v>
@@ -80125,6 +80125,35 @@
         <v>64075</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.361000001430511</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.351000010967255</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.351000010967255</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>240507</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.351000010967255</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.361000001430511</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.344999998807907</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>180978</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80186,6 +80186,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.363999992609024</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.361999988555908</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>68639</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GAB.MI.xlsx
+++ b/data/GAB.MI.xlsx
@@ -80215,6 +80215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.386999994516373</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.361999988555908</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.384999990463257</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>121600</v>
+      </c>
+      <c r="I2754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
